--- a/r4-ELGA-e-Medikation-Review_Architektur/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-Review_Architektur/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:41:29+00:00</t>
+    <t>2026-06-22T13:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2027,7 +2027,7 @@
     <t>AT ELGA e-Medikation Medication Medikation</t>
   </si>
   <si>
-    <t>Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe.</t>
+    <t>Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, Geplanter Abgabe und Durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Medication</t>
@@ -2377,7 +2377,7 @@
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -2393,7 +2393,7 @@
 </t>
   </si>
   <si>
-    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>
@@ -2402,7 +2402,7 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
+    <t>Status der Durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die Durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die Durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
   </si>
   <si>
     <t>A code specifying the state of the set of dispense events.</t>
@@ -2448,13 +2448,13 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>MedicationDispense.category</t>
   </si>
   <si>
-    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the type of medication dispense (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -2489,7 +2489,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t>Patient, für den die durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+    <t>Patient, für den die Durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
@@ -2505,7 +2505,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Encounter oder EpisodeOfCare. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz auf Encounter oder EpisodeOfCare. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The encounter or episode of care that establishes the context for this event.</t>
@@ -2518,7 +2518,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Additional information that supports the medication being dispensed.</t>
@@ -2545,7 +2545,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -2568,7 +2568,7 @@
   </si>
   <si>
     <t>Refrenz auf Practitioner, PractitionerRole, Organization, 
-der/die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
+der/die die Durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
 auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
@@ -2595,9 +2595,9 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert bzw. 
-Planeintrag (MedicationRequest). Es muss nicht zwingend eine geplante Abgabe referenziert werden, da es auch durchgeführte 
-Abgaben ohne geplante Abgabe geben kann (z.B. Notfall oder OTC-Medikation).</t>
+    <t>Referenz auf zugehörige Geplante Abgabe (MedicationRequest), sofern diese existiert bzw. 
+Planeintrag (MedicationRequest). Es muss nicht zwingend eine Geplante Abgabe referenziert werden, da es auch durchgeführte 
+Abgaben ohne Geplante Abgabe geben kann (z.B. Notfall oder OTC-Medikation).</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -2919,7 +2919,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, geplante Abgabe | completed: geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
+    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, Geplante Abgabe | completed: Geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -2949,7 +2949,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Die geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
+    <t>Die Geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -3044,7 +3044,7 @@
     <t>MedicationRequest.doNotPerform</t>
   </si>
   <si>
-    <t>Gibt an, ob die geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Gibt an, ob die Geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -3082,7 +3082,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t>Patient, für den die geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+    <t>Patient, für den die Geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -3094,7 +3094,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t>Aufenthalt/Begegnung, während dessen die geplante Abgabe erstellt wurde. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Aufenthalt/Begegnung, während dessen die Geplante Abgabe erstellt wurde. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -3126,7 +3126,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
+    <t>Der Arzt oder die Ärztin, die die Geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
 (eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
@@ -3231,7 +3231,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese geplante Abgabe basiert.</t>
+    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese Geplante Abgabe basiert.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -3242,7 +3242,7 @@
   <si>
     <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
 Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine 
-geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
+Geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -3381,10 +3381,10 @@
 </t>
   </si>
   <si>
-    <t>Gültigkeitszeitraum einer geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
-  </si>
-  <si>
-    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann.
+    <t>Gültigkeitszeitraum einer Geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
+  </si>
+  <si>
+    <t>Zeitraum in dem die Geplante Abgabe eingelöst werden kann.
 Der Gültigkeitszeitraum ist abhängig von der **Rezeptart**: 
 * **Kassenrezept**: ab Erstelldatum einen Monat gültig (vom Ausstellungszeitpunkt bis zum gleichen Tag des Folgemonats 23:59 Uhr); validityPeriod.start kein Datum in der Zukunft; bei einer Teilabgabe verlängert sich die gesamte Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess).
 * **Privatrezept**: ab Erstelldatum maximal 365 Tage gültig, wenn die erste Einlösung innerhalb von 1 Monat ab Erstelldatum erfolgt (sonst Status abgelaufen). validityPeriod.start kein Datum in der Zukunft; Die Gültigkeitsdauer (validityPeriod.end) kann vom Arzt definiert werden.
@@ -3465,7 +3465,7 @@
     <t>MedicationRequest.dispenseRequest.performer</t>
   </si>
   <si>
-    <t>Apotheke oder andere Einrichtung, die die geplante Abgabe einlösen soll. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Apotheke oder andere Einrichtung, die die Geplante Abgabe einlösen soll. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the intended dispensing Organization specified by the prescriber.</t>
@@ -3474,7 +3474,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die Geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -3520,7 +3520,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t>Im Falle einer Änderung wird auf die ersetzte geplante Abgabe verwiesen. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Im Falle einer Änderung wird auf die ersetzte Geplante Abgabe verwiesen. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>
@@ -3625,7 +3625,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
+    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine Geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
